--- a/Sindhi Muslim/Student Attendance/home/Class 5- Monthly Attendance - Aug to Nov.xlsx
+++ b/Sindhi Muslim/Student Attendance/home/Class 5- Monthly Attendance - Aug to Nov.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\Student Attendance\home\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0562FEB5-0D21-4844-8D6D-05CDA4AC9C73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D63E069D-442C-4A19-BB85-38E07CE30037}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="10920" tabRatio="626" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="626" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="August" sheetId="23" r:id="rId1"/>
-    <sheet name="September" sheetId="28" r:id="rId2"/>
-    <sheet name="October" sheetId="29" r:id="rId3"/>
-    <sheet name="November" sheetId="30" r:id="rId4"/>
+    <sheet name="August-2024" sheetId="23" r:id="rId1"/>
+    <sheet name="September-2024" sheetId="28" r:id="rId2"/>
+    <sheet name="October-2024" sheetId="29" r:id="rId3"/>
+    <sheet name="November-2024" sheetId="30" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4578" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4578" uniqueCount="133">
   <si>
     <t>S.No</t>
   </si>
@@ -428,6 +428,15 @@
   <si>
     <t>IQBAL DAY - IQBAL DAY - IQBAL DAY - IQBAL DAY</t>
   </si>
+  <si>
+    <t>Monthly Attendence Month of November-2024</t>
+  </si>
+  <si>
+    <t>Monthly Attendence Month of October-2024</t>
+  </si>
+  <si>
+    <t>Monthly Attendence Month of September-2024</t>
+  </si>
 </sst>
 </file>
 
@@ -710,6 +719,21 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
@@ -726,21 +750,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="17" fontId="8" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1512,75 +1521,75 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
-      <c r="J1" s="28"/>
-      <c r="K1" s="28"/>
-      <c r="L1" s="28"/>
-      <c r="M1" s="28"/>
-      <c r="N1" s="28"/>
-      <c r="O1" s="28"/>
-      <c r="P1" s="28"/>
-      <c r="Q1" s="28"/>
-      <c r="R1" s="28"/>
-      <c r="S1" s="28"/>
-      <c r="T1" s="28"/>
-      <c r="U1" s="28"/>
-      <c r="V1" s="28"/>
-      <c r="W1" s="28"/>
-      <c r="X1" s="28"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="22"/>
+      <c r="L1" s="22"/>
+      <c r="M1" s="22"/>
+      <c r="N1" s="22"/>
+      <c r="O1" s="22"/>
+      <c r="P1" s="22"/>
+      <c r="Q1" s="22"/>
+      <c r="R1" s="22"/>
+      <c r="S1" s="22"/>
+      <c r="T1" s="22"/>
+      <c r="U1" s="22"/>
+      <c r="V1" s="22"/>
+      <c r="W1" s="22"/>
+      <c r="X1" s="22"/>
     </row>
     <row r="2" spans="1:28" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
-      <c r="I2" s="29"/>
-      <c r="J2" s="29"/>
-      <c r="K2" s="29"/>
-      <c r="L2" s="29"/>
-      <c r="M2" s="29"/>
-      <c r="N2" s="29"/>
-      <c r="O2" s="29"/>
-      <c r="P2" s="29"/>
-      <c r="Q2" s="29"/>
-      <c r="R2" s="29"/>
-      <c r="S2" s="29"/>
-      <c r="T2" s="29"/>
-      <c r="U2" s="29"/>
-      <c r="V2" s="29"/>
-      <c r="W2" s="29"/>
-      <c r="X2" s="29"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
+      <c r="I2" s="23"/>
+      <c r="J2" s="23"/>
+      <c r="K2" s="23"/>
+      <c r="L2" s="23"/>
+      <c r="M2" s="23"/>
+      <c r="N2" s="23"/>
+      <c r="O2" s="23"/>
+      <c r="P2" s="23"/>
+      <c r="Q2" s="23"/>
+      <c r="R2" s="23"/>
+      <c r="S2" s="23"/>
+      <c r="T2" s="23"/>
+      <c r="U2" s="23"/>
+      <c r="V2" s="23"/>
+      <c r="W2" s="23"/>
+      <c r="X2" s="23"/>
     </row>
     <row r="3" spans="1:28" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="30" t="s">
+      <c r="A3" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="30" t="s">
+      <c r="B3" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="30" t="s">
+      <c r="C3" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="30" t="s">
+      <c r="D3" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="30" t="s">
+      <c r="E3" s="24" t="s">
         <v>4</v>
       </c>
       <c r="F3" s="2" t="str">
@@ -1651,25 +1660,25 @@
         <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
-      <c r="W3" s="32" t="s">
+      <c r="W3" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="X3" s="32" t="s">
+      <c r="X3" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="Y3" s="25" t="s">
+      <c r="Y3" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="Z3" s="26"/>
+      <c r="Z3" s="31"/>
       <c r="AA3" s="3"/>
       <c r="AB3" s="3"/>
     </row>
     <row r="4" spans="1:28" ht="36.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="31"/>
-      <c r="B4" s="31"/>
-      <c r="C4" s="31"/>
-      <c r="D4" s="31"/>
-      <c r="E4" s="31"/>
+      <c r="A4" s="25"/>
+      <c r="B4" s="25"/>
+      <c r="C4" s="25"/>
+      <c r="D4" s="25"/>
+      <c r="E4" s="25"/>
       <c r="F4" s="14">
         <v>45519</v>
       </c>
@@ -1721,8 +1730,8 @@
       <c r="V4" s="14">
         <v>45535</v>
       </c>
-      <c r="W4" s="32"/>
-      <c r="X4" s="32"/>
+      <c r="W4" s="26"/>
+      <c r="X4" s="26"/>
       <c r="Y4" s="4" t="s">
         <v>7</v>
       </c>
@@ -1761,7 +1770,7 @@
         <v>123</v>
       </c>
       <c r="J5" s="17"/>
-      <c r="K5" s="22" t="s">
+      <c r="K5" s="27" t="s">
         <v>124</v>
       </c>
       <c r="L5" s="17"/>
@@ -1771,13 +1780,13 @@
       <c r="P5" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="Q5" s="22" t="s">
+      <c r="Q5" s="27" t="s">
         <v>126</v>
       </c>
       <c r="R5" s="17"/>
       <c r="S5" s="17"/>
       <c r="T5" s="17"/>
-      <c r="U5" s="22" t="s">
+      <c r="U5" s="27" t="s">
         <v>125</v>
       </c>
       <c r="V5" s="17"/>
@@ -1829,7 +1838,7 @@
       <c r="J6" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="K6" s="23"/>
+      <c r="K6" s="28"/>
       <c r="L6" s="17" t="s">
         <v>31</v>
       </c>
@@ -1843,7 +1852,7 @@
         <v>23</v>
       </c>
       <c r="P6" s="20"/>
-      <c r="Q6" s="23"/>
+      <c r="Q6" s="28"/>
       <c r="R6" s="17" t="s">
         <v>23</v>
       </c>
@@ -1853,7 +1862,7 @@
       <c r="T6" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="U6" s="23"/>
+      <c r="U6" s="28"/>
       <c r="V6" s="17"/>
       <c r="W6" s="5">
         <f t="shared" si="1"/>
@@ -1901,7 +1910,7 @@
       <c r="J7" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="K7" s="23"/>
+      <c r="K7" s="28"/>
       <c r="L7" s="17" t="s">
         <v>23</v>
       </c>
@@ -1915,7 +1924,7 @@
         <v>23</v>
       </c>
       <c r="P7" s="20"/>
-      <c r="Q7" s="23"/>
+      <c r="Q7" s="28"/>
       <c r="R7" s="17" t="s">
         <v>23</v>
       </c>
@@ -1925,7 +1934,7 @@
       <c r="T7" s="17" t="s">
         <v>127</v>
       </c>
-      <c r="U7" s="23"/>
+      <c r="U7" s="28"/>
       <c r="V7" s="17"/>
       <c r="W7" s="5">
         <f t="shared" si="1"/>
@@ -1969,7 +1978,7 @@
       <c r="J8" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="K8" s="23"/>
+      <c r="K8" s="28"/>
       <c r="L8" s="17" t="s">
         <v>23</v>
       </c>
@@ -1983,7 +1992,7 @@
         <v>31</v>
       </c>
       <c r="P8" s="20"/>
-      <c r="Q8" s="23"/>
+      <c r="Q8" s="28"/>
       <c r="R8" s="17" t="s">
         <v>31</v>
       </c>
@@ -1993,7 +2002,7 @@
       <c r="T8" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="U8" s="23"/>
+      <c r="U8" s="28"/>
       <c r="V8" s="17"/>
       <c r="W8" s="5">
         <f t="shared" si="1"/>
@@ -2003,12 +2012,12 @@
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="Y8" s="25" t="s">
+      <c r="Y8" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="Z8" s="26"/>
-      <c r="AA8" s="26"/>
-      <c r="AB8" s="27"/>
+      <c r="Z8" s="31"/>
+      <c r="AA8" s="31"/>
+      <c r="AB8" s="32"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
@@ -2039,7 +2048,7 @@
       <c r="J9" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="K9" s="23"/>
+      <c r="K9" s="28"/>
       <c r="L9" s="17" t="s">
         <v>23</v>
       </c>
@@ -2053,7 +2062,7 @@
         <v>23</v>
       </c>
       <c r="P9" s="20"/>
-      <c r="Q9" s="23"/>
+      <c r="Q9" s="28"/>
       <c r="R9" s="17" t="s">
         <v>23</v>
       </c>
@@ -2063,7 +2072,7 @@
       <c r="T9" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="U9" s="23"/>
+      <c r="U9" s="28"/>
       <c r="V9" s="17"/>
       <c r="W9" s="5">
         <f t="shared" si="1"/>
@@ -2115,7 +2124,7 @@
       <c r="J10" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="K10" s="23"/>
+      <c r="K10" s="28"/>
       <c r="L10" s="17" t="s">
         <v>31</v>
       </c>
@@ -2129,7 +2138,7 @@
         <v>31</v>
       </c>
       <c r="P10" s="20"/>
-      <c r="Q10" s="23"/>
+      <c r="Q10" s="28"/>
       <c r="R10" s="17" t="s">
         <v>31</v>
       </c>
@@ -2139,7 +2148,7 @@
       <c r="T10" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="U10" s="23"/>
+      <c r="U10" s="28"/>
       <c r="V10" s="17"/>
       <c r="W10" s="5">
         <f t="shared" si="1"/>
@@ -2194,7 +2203,7 @@
       <c r="J11" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="K11" s="23"/>
+      <c r="K11" s="28"/>
       <c r="L11" s="17" t="s">
         <v>23</v>
       </c>
@@ -2208,7 +2217,7 @@
         <v>23</v>
       </c>
       <c r="P11" s="20"/>
-      <c r="Q11" s="23"/>
+      <c r="Q11" s="28"/>
       <c r="R11" s="17" t="s">
         <v>23</v>
       </c>
@@ -2218,7 +2227,7 @@
       <c r="T11" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="U11" s="23"/>
+      <c r="U11" s="28"/>
       <c r="V11" s="17"/>
       <c r="W11" s="5">
         <f t="shared" si="1"/>
@@ -2273,7 +2282,7 @@
       <c r="J12" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="K12" s="23"/>
+      <c r="K12" s="28"/>
       <c r="L12" s="17" t="s">
         <v>23</v>
       </c>
@@ -2287,7 +2296,7 @@
         <v>31</v>
       </c>
       <c r="P12" s="20"/>
-      <c r="Q12" s="23"/>
+      <c r="Q12" s="28"/>
       <c r="R12" s="17" t="s">
         <v>31</v>
       </c>
@@ -2297,7 +2306,7 @@
       <c r="T12" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="U12" s="23"/>
+      <c r="U12" s="28"/>
       <c r="V12" s="17"/>
       <c r="W12" s="5">
         <f t="shared" si="1"/>
@@ -2352,7 +2361,7 @@
       <c r="J13" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="K13" s="23"/>
+      <c r="K13" s="28"/>
       <c r="L13" s="17" t="s">
         <v>31</v>
       </c>
@@ -2366,7 +2375,7 @@
         <v>23</v>
       </c>
       <c r="P13" s="20"/>
-      <c r="Q13" s="23"/>
+      <c r="Q13" s="28"/>
       <c r="R13" s="17" t="s">
         <v>23</v>
       </c>
@@ -2376,7 +2385,7 @@
       <c r="T13" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="U13" s="23"/>
+      <c r="U13" s="28"/>
       <c r="V13" s="17"/>
       <c r="W13" s="5">
         <f t="shared" si="1"/>
@@ -2420,7 +2429,7 @@
       <c r="J14" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="K14" s="23"/>
+      <c r="K14" s="28"/>
       <c r="L14" s="17" t="s">
         <v>23</v>
       </c>
@@ -2434,7 +2443,7 @@
         <v>23</v>
       </c>
       <c r="P14" s="20"/>
-      <c r="Q14" s="23"/>
+      <c r="Q14" s="28"/>
       <c r="R14" s="17" t="s">
         <v>31</v>
       </c>
@@ -2444,7 +2453,7 @@
       <c r="T14" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="U14" s="23"/>
+      <c r="U14" s="28"/>
       <c r="V14" s="17"/>
       <c r="W14" s="5">
         <f t="shared" si="1"/>
@@ -2488,7 +2497,7 @@
       <c r="J15" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="K15" s="23"/>
+      <c r="K15" s="28"/>
       <c r="L15" s="17" t="s">
         <v>23</v>
       </c>
@@ -2502,7 +2511,7 @@
         <v>23</v>
       </c>
       <c r="P15" s="20"/>
-      <c r="Q15" s="23"/>
+      <c r="Q15" s="28"/>
       <c r="R15" s="17" t="s">
         <v>31</v>
       </c>
@@ -2512,7 +2521,7 @@
       <c r="T15" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="U15" s="23"/>
+      <c r="U15" s="28"/>
       <c r="V15" s="17"/>
       <c r="W15" s="5">
         <f t="shared" si="1"/>
@@ -2556,7 +2565,7 @@
       <c r="J16" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="K16" s="23"/>
+      <c r="K16" s="28"/>
       <c r="L16" s="17" t="s">
         <v>23</v>
       </c>
@@ -2570,7 +2579,7 @@
         <v>23</v>
       </c>
       <c r="P16" s="20"/>
-      <c r="Q16" s="23"/>
+      <c r="Q16" s="28"/>
       <c r="R16" s="17" t="s">
         <v>23</v>
       </c>
@@ -2580,7 +2589,7 @@
       <c r="T16" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="U16" s="23"/>
+      <c r="U16" s="28"/>
       <c r="V16" s="17"/>
       <c r="W16" s="5">
         <f t="shared" si="1"/>
@@ -2590,12 +2599,12 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="Y16" s="25" t="s">
+      <c r="Y16" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="Z16" s="26"/>
-      <c r="AA16" s="26"/>
-      <c r="AB16" s="27"/>
+      <c r="Z16" s="31"/>
+      <c r="AA16" s="31"/>
+      <c r="AB16" s="32"/>
     </row>
     <row r="17" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
@@ -2626,7 +2635,7 @@
       <c r="J17" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="K17" s="23"/>
+      <c r="K17" s="28"/>
       <c r="L17" s="17" t="s">
         <v>23</v>
       </c>
@@ -2640,7 +2649,7 @@
         <v>23</v>
       </c>
       <c r="P17" s="20"/>
-      <c r="Q17" s="23"/>
+      <c r="Q17" s="28"/>
       <c r="R17" s="17" t="s">
         <v>31</v>
       </c>
@@ -2650,7 +2659,7 @@
       <c r="T17" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="U17" s="23"/>
+      <c r="U17" s="28"/>
       <c r="V17" s="17"/>
       <c r="W17" s="5">
         <f t="shared" si="1"/>
@@ -2702,7 +2711,7 @@
       <c r="J18" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="K18" s="23"/>
+      <c r="K18" s="28"/>
       <c r="L18" s="17" t="s">
         <v>23</v>
       </c>
@@ -2716,7 +2725,7 @@
         <v>23</v>
       </c>
       <c r="P18" s="20"/>
-      <c r="Q18" s="23"/>
+      <c r="Q18" s="28"/>
       <c r="R18" s="17" t="s">
         <v>31</v>
       </c>
@@ -2726,7 +2735,7 @@
       <c r="T18" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="U18" s="23"/>
+      <c r="U18" s="28"/>
       <c r="V18" s="17"/>
       <c r="W18" s="5">
         <f t="shared" si="1"/>
@@ -2781,7 +2790,7 @@
       <c r="J19" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="K19" s="23"/>
+      <c r="K19" s="28"/>
       <c r="L19" s="17" t="s">
         <v>31</v>
       </c>
@@ -2795,7 +2804,7 @@
         <v>31</v>
       </c>
       <c r="P19" s="20"/>
-      <c r="Q19" s="23"/>
+      <c r="Q19" s="28"/>
       <c r="R19" s="17" t="s">
         <v>23</v>
       </c>
@@ -2805,7 +2814,7 @@
       <c r="T19" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="U19" s="23"/>
+      <c r="U19" s="28"/>
       <c r="V19" s="17"/>
       <c r="W19" s="5">
         <f t="shared" si="1"/>
@@ -2860,7 +2869,7 @@
       <c r="J20" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="K20" s="23"/>
+      <c r="K20" s="28"/>
       <c r="L20" s="17" t="s">
         <v>23</v>
       </c>
@@ -2874,7 +2883,7 @@
         <v>23</v>
       </c>
       <c r="P20" s="20"/>
-      <c r="Q20" s="23"/>
+      <c r="Q20" s="28"/>
       <c r="R20" s="17" t="s">
         <v>23</v>
       </c>
@@ -2884,7 +2893,7 @@
       <c r="T20" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="U20" s="23"/>
+      <c r="U20" s="28"/>
       <c r="V20" s="17"/>
       <c r="W20" s="5">
         <f t="shared" si="1"/>
@@ -2928,7 +2937,7 @@
       <c r="J21" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="K21" s="23"/>
+      <c r="K21" s="28"/>
       <c r="L21" s="17" t="s">
         <v>23</v>
       </c>
@@ -2942,7 +2951,7 @@
         <v>31</v>
       </c>
       <c r="P21" s="20"/>
-      <c r="Q21" s="23"/>
+      <c r="Q21" s="28"/>
       <c r="R21" s="17" t="s">
         <v>31</v>
       </c>
@@ -2952,7 +2961,7 @@
       <c r="T21" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="U21" s="23"/>
+      <c r="U21" s="28"/>
       <c r="V21" s="17"/>
       <c r="W21" s="5">
         <f t="shared" si="1"/>
@@ -3007,7 +3016,7 @@
       <c r="J22" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="K22" s="23"/>
+      <c r="K22" s="28"/>
       <c r="L22" s="17" t="s">
         <v>23</v>
       </c>
@@ -3021,7 +3030,7 @@
         <v>23</v>
       </c>
       <c r="P22" s="20"/>
-      <c r="Q22" s="23"/>
+      <c r="Q22" s="28"/>
       <c r="R22" s="17" t="s">
         <v>23</v>
       </c>
@@ -3031,7 +3040,7 @@
       <c r="T22" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="U22" s="23"/>
+      <c r="U22" s="28"/>
       <c r="V22" s="17"/>
       <c r="W22" s="5">
         <f t="shared" si="1"/>
@@ -3071,7 +3080,7 @@
       <c r="J23" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="K23" s="23"/>
+      <c r="K23" s="28"/>
       <c r="L23" s="17" t="s">
         <v>23</v>
       </c>
@@ -3085,7 +3094,7 @@
         <v>23</v>
       </c>
       <c r="P23" s="20"/>
-      <c r="Q23" s="23"/>
+      <c r="Q23" s="28"/>
       <c r="R23" s="17" t="s">
         <v>31</v>
       </c>
@@ -3095,7 +3104,7 @@
       <c r="T23" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="U23" s="23"/>
+      <c r="U23" s="28"/>
       <c r="V23" s="17"/>
       <c r="W23" s="5">
         <f t="shared" si="1"/>
@@ -3135,7 +3144,7 @@
       <c r="J24" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="K24" s="23"/>
+      <c r="K24" s="28"/>
       <c r="L24" s="17" t="s">
         <v>23</v>
       </c>
@@ -3149,7 +3158,7 @@
         <v>23</v>
       </c>
       <c r="P24" s="20"/>
-      <c r="Q24" s="23"/>
+      <c r="Q24" s="28"/>
       <c r="R24" s="17" t="s">
         <v>23</v>
       </c>
@@ -3159,7 +3168,7 @@
       <c r="T24" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="U24" s="23"/>
+      <c r="U24" s="28"/>
       <c r="V24" s="17"/>
       <c r="W24" s="5">
         <f t="shared" si="1"/>
@@ -3199,7 +3208,7 @@
       <c r="J25" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="K25" s="23"/>
+      <c r="K25" s="28"/>
       <c r="L25" s="17" t="s">
         <v>31</v>
       </c>
@@ -3213,7 +3222,7 @@
         <v>31</v>
       </c>
       <c r="P25" s="20"/>
-      <c r="Q25" s="23"/>
+      <c r="Q25" s="28"/>
       <c r="R25" s="17" t="s">
         <v>31</v>
       </c>
@@ -3223,7 +3232,7 @@
       <c r="T25" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="U25" s="23"/>
+      <c r="U25" s="28"/>
       <c r="V25" s="17"/>
       <c r="W25" s="5">
         <f t="shared" si="1"/>
@@ -3263,7 +3272,7 @@
       <c r="J26" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="K26" s="23"/>
+      <c r="K26" s="28"/>
       <c r="L26" s="17" t="s">
         <v>31</v>
       </c>
@@ -3277,7 +3286,7 @@
         <v>31</v>
       </c>
       <c r="P26" s="20"/>
-      <c r="Q26" s="23"/>
+      <c r="Q26" s="28"/>
       <c r="R26" s="17" t="s">
         <v>23</v>
       </c>
@@ -3287,7 +3296,7 @@
       <c r="T26" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="U26" s="23"/>
+      <c r="U26" s="28"/>
       <c r="V26" s="17"/>
       <c r="W26" s="5">
         <f t="shared" si="1"/>
@@ -3327,7 +3336,7 @@
       <c r="J27" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="K27" s="23"/>
+      <c r="K27" s="28"/>
       <c r="L27" s="17" t="s">
         <v>23</v>
       </c>
@@ -3341,7 +3350,7 @@
         <v>23</v>
       </c>
       <c r="P27" s="20"/>
-      <c r="Q27" s="23"/>
+      <c r="Q27" s="28"/>
       <c r="R27" s="17" t="s">
         <v>31</v>
       </c>
@@ -3351,7 +3360,7 @@
       <c r="T27" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="U27" s="23"/>
+      <c r="U27" s="28"/>
       <c r="V27" s="17"/>
       <c r="W27" s="5">
         <f t="shared" si="1"/>
@@ -3391,7 +3400,7 @@
       <c r="J28" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="K28" s="23"/>
+      <c r="K28" s="28"/>
       <c r="L28" s="17" t="s">
         <v>31</v>
       </c>
@@ -3405,7 +3414,7 @@
         <v>23</v>
       </c>
       <c r="P28" s="20"/>
-      <c r="Q28" s="23"/>
+      <c r="Q28" s="28"/>
       <c r="R28" s="17" t="s">
         <v>23</v>
       </c>
@@ -3415,7 +3424,7 @@
       <c r="T28" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="U28" s="23"/>
+      <c r="U28" s="28"/>
       <c r="V28" s="17"/>
       <c r="W28" s="5">
         <f t="shared" si="1"/>
@@ -3455,7 +3464,7 @@
       <c r="J29" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="K29" s="23"/>
+      <c r="K29" s="28"/>
       <c r="L29" s="17" t="s">
         <v>31</v>
       </c>
@@ -3469,7 +3478,7 @@
         <v>23</v>
       </c>
       <c r="P29" s="20"/>
-      <c r="Q29" s="23"/>
+      <c r="Q29" s="28"/>
       <c r="R29" s="17" t="s">
         <v>23</v>
       </c>
@@ -3479,7 +3488,7 @@
       <c r="T29" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="U29" s="23"/>
+      <c r="U29" s="28"/>
       <c r="V29" s="17"/>
       <c r="W29" s="5">
         <f t="shared" si="1"/>
@@ -3517,17 +3526,17 @@
       </c>
       <c r="I30" s="20"/>
       <c r="J30" s="17"/>
-      <c r="K30" s="23"/>
+      <c r="K30" s="28"/>
       <c r="L30" s="17"/>
       <c r="M30" s="17"/>
       <c r="N30" s="17"/>
       <c r="O30" s="17"/>
       <c r="P30" s="20"/>
-      <c r="Q30" s="23"/>
+      <c r="Q30" s="28"/>
       <c r="R30" s="17"/>
       <c r="S30" s="17"/>
       <c r="T30" s="17"/>
-      <c r="U30" s="23"/>
+      <c r="U30" s="28"/>
       <c r="V30" s="17"/>
       <c r="W30" s="5">
         <f t="shared" si="1"/>
@@ -3567,7 +3576,7 @@
       <c r="J31" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="K31" s="23"/>
+      <c r="K31" s="28"/>
       <c r="L31" s="17" t="s">
         <v>23</v>
       </c>
@@ -3581,7 +3590,7 @@
         <v>23</v>
       </c>
       <c r="P31" s="20"/>
-      <c r="Q31" s="23"/>
+      <c r="Q31" s="28"/>
       <c r="R31" s="17" t="s">
         <v>23</v>
       </c>
@@ -3591,7 +3600,7 @@
       <c r="T31" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="U31" s="23"/>
+      <c r="U31" s="28"/>
       <c r="V31" s="17"/>
       <c r="W31" s="5">
         <f t="shared" si="1"/>
@@ -3631,7 +3640,7 @@
       <c r="J32" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="K32" s="23"/>
+      <c r="K32" s="28"/>
       <c r="L32" s="17" t="s">
         <v>23</v>
       </c>
@@ -3645,7 +3654,7 @@
         <v>23</v>
       </c>
       <c r="P32" s="20"/>
-      <c r="Q32" s="23"/>
+      <c r="Q32" s="28"/>
       <c r="R32" s="17" t="s">
         <v>32</v>
       </c>
@@ -3655,7 +3664,7 @@
       <c r="T32" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="U32" s="23"/>
+      <c r="U32" s="28"/>
       <c r="V32" s="17"/>
       <c r="W32" s="5">
         <f t="shared" si="1"/>
@@ -3695,7 +3704,7 @@
       <c r="J33" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="K33" s="23"/>
+      <c r="K33" s="28"/>
       <c r="L33" s="17" t="s">
         <v>23</v>
       </c>
@@ -3709,7 +3718,7 @@
         <v>23</v>
       </c>
       <c r="P33" s="20"/>
-      <c r="Q33" s="23"/>
+      <c r="Q33" s="28"/>
       <c r="R33" s="17" t="s">
         <v>23</v>
       </c>
@@ -3719,7 +3728,7 @@
       <c r="T33" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="U33" s="23"/>
+      <c r="U33" s="28"/>
       <c r="V33" s="17"/>
       <c r="W33" s="5">
         <f t="shared" si="1"/>
@@ -3759,7 +3768,7 @@
       <c r="J34" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="K34" s="23"/>
+      <c r="K34" s="28"/>
       <c r="L34" s="17" t="s">
         <v>23</v>
       </c>
@@ -3773,7 +3782,7 @@
         <v>23</v>
       </c>
       <c r="P34" s="20"/>
-      <c r="Q34" s="23"/>
+      <c r="Q34" s="28"/>
       <c r="R34" s="17" t="s">
         <v>31</v>
       </c>
@@ -3783,7 +3792,7 @@
       <c r="T34" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="U34" s="23"/>
+      <c r="U34" s="28"/>
       <c r="V34" s="17"/>
       <c r="W34" s="5">
         <f t="shared" si="1"/>
@@ -3823,7 +3832,7 @@
       <c r="J35" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="K35" s="23"/>
+      <c r="K35" s="28"/>
       <c r="L35" s="17" t="s">
         <v>23</v>
       </c>
@@ -3837,7 +3846,7 @@
         <v>23</v>
       </c>
       <c r="P35" s="20"/>
-      <c r="Q35" s="23"/>
+      <c r="Q35" s="28"/>
       <c r="R35" s="17" t="s">
         <v>23</v>
       </c>
@@ -3847,7 +3856,7 @@
       <c r="T35" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="U35" s="23"/>
+      <c r="U35" s="28"/>
       <c r="V35" s="17"/>
       <c r="W35" s="5">
         <f t="shared" si="1"/>
@@ -3885,7 +3894,7 @@
       <c r="J36" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="K36" s="23"/>
+      <c r="K36" s="28"/>
       <c r="L36" s="17" t="s">
         <v>23</v>
       </c>
@@ -3899,7 +3908,7 @@
         <v>23</v>
       </c>
       <c r="P36" s="20"/>
-      <c r="Q36" s="23"/>
+      <c r="Q36" s="28"/>
       <c r="R36" s="17" t="s">
         <v>23</v>
       </c>
@@ -3909,7 +3918,7 @@
       <c r="T36" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="U36" s="23"/>
+      <c r="U36" s="28"/>
       <c r="V36" s="17"/>
       <c r="W36" s="5">
         <f t="shared" si="1"/>
@@ -3949,7 +3958,7 @@
       <c r="J37" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="K37" s="23"/>
+      <c r="K37" s="28"/>
       <c r="L37" s="17" t="s">
         <v>23</v>
       </c>
@@ -3963,7 +3972,7 @@
         <v>23</v>
       </c>
       <c r="P37" s="20"/>
-      <c r="Q37" s="23"/>
+      <c r="Q37" s="28"/>
       <c r="R37" s="17" t="s">
         <v>31</v>
       </c>
@@ -3973,10 +3982,10 @@
       <c r="T37" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="U37" s="23"/>
+      <c r="U37" s="28"/>
       <c r="V37" s="17"/>
       <c r="W37" s="5">
-        <f t="shared" ref="W37:W68" si="3">COUNTIF(F37:V37,"P")</f>
+        <f t="shared" ref="W37:W53" si="3">COUNTIF(F37:V37,"P")</f>
         <v>4</v>
       </c>
       <c r="X37" s="5">
@@ -4013,7 +4022,7 @@
       <c r="J38" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="K38" s="23"/>
+      <c r="K38" s="28"/>
       <c r="L38" s="17" t="s">
         <v>23</v>
       </c>
@@ -4027,7 +4036,7 @@
         <v>23</v>
       </c>
       <c r="P38" s="20"/>
-      <c r="Q38" s="23"/>
+      <c r="Q38" s="28"/>
       <c r="R38" s="17" t="s">
         <v>23</v>
       </c>
@@ -4037,7 +4046,7 @@
       <c r="T38" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="U38" s="23"/>
+      <c r="U38" s="28"/>
       <c r="V38" s="17"/>
       <c r="W38" s="5">
         <f t="shared" si="3"/>
@@ -4077,7 +4086,7 @@
       <c r="J39" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="K39" s="23"/>
+      <c r="K39" s="28"/>
       <c r="L39" s="17" t="s">
         <v>23</v>
       </c>
@@ -4091,7 +4100,7 @@
         <v>23</v>
       </c>
       <c r="P39" s="20"/>
-      <c r="Q39" s="23"/>
+      <c r="Q39" s="28"/>
       <c r="R39" s="17" t="s">
         <v>23</v>
       </c>
@@ -4101,7 +4110,7 @@
       <c r="T39" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="U39" s="23"/>
+      <c r="U39" s="28"/>
       <c r="V39" s="17"/>
       <c r="W39" s="5">
         <f t="shared" si="3"/>
@@ -4141,7 +4150,7 @@
       <c r="J40" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="K40" s="23"/>
+      <c r="K40" s="28"/>
       <c r="L40" s="17" t="s">
         <v>23</v>
       </c>
@@ -4155,7 +4164,7 @@
         <v>23</v>
       </c>
       <c r="P40" s="20"/>
-      <c r="Q40" s="23"/>
+      <c r="Q40" s="28"/>
       <c r="R40" s="17" t="s">
         <v>23</v>
       </c>
@@ -4165,7 +4174,7 @@
       <c r="T40" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="U40" s="23"/>
+      <c r="U40" s="28"/>
       <c r="V40" s="17"/>
       <c r="W40" s="5">
         <f t="shared" si="3"/>
@@ -4205,7 +4214,7 @@
       <c r="J41" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="K41" s="23"/>
+      <c r="K41" s="28"/>
       <c r="L41" s="17" t="s">
         <v>23</v>
       </c>
@@ -4219,7 +4228,7 @@
         <v>23</v>
       </c>
       <c r="P41" s="20"/>
-      <c r="Q41" s="23"/>
+      <c r="Q41" s="28"/>
       <c r="R41" s="17" t="s">
         <v>23</v>
       </c>
@@ -4229,7 +4238,7 @@
       <c r="T41" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="U41" s="23"/>
+      <c r="U41" s="28"/>
       <c r="V41" s="17"/>
       <c r="W41" s="5">
         <f t="shared" si="3"/>
@@ -4269,7 +4278,7 @@
       <c r="J42" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="K42" s="23"/>
+      <c r="K42" s="28"/>
       <c r="L42" s="17" t="s">
         <v>23</v>
       </c>
@@ -4283,7 +4292,7 @@
         <v>23</v>
       </c>
       <c r="P42" s="20"/>
-      <c r="Q42" s="23"/>
+      <c r="Q42" s="28"/>
       <c r="R42" s="17" t="s">
         <v>23</v>
       </c>
@@ -4293,7 +4302,7 @@
       <c r="T42" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="U42" s="23"/>
+      <c r="U42" s="28"/>
       <c r="V42" s="17"/>
       <c r="W42" s="5">
         <f t="shared" si="3"/>
@@ -4333,7 +4342,7 @@
       <c r="J43" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="K43" s="23"/>
+      <c r="K43" s="28"/>
       <c r="L43" s="17" t="s">
         <v>23</v>
       </c>
@@ -4347,7 +4356,7 @@
         <v>23</v>
       </c>
       <c r="P43" s="20"/>
-      <c r="Q43" s="23"/>
+      <c r="Q43" s="28"/>
       <c r="R43" s="17" t="s">
         <v>23</v>
       </c>
@@ -4357,7 +4366,7 @@
       <c r="T43" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="U43" s="23"/>
+      <c r="U43" s="28"/>
       <c r="V43" s="17"/>
       <c r="W43" s="5">
         <f t="shared" si="3"/>
@@ -4397,7 +4406,7 @@
       <c r="J44" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="K44" s="23"/>
+      <c r="K44" s="28"/>
       <c r="L44" s="17" t="s">
         <v>23</v>
       </c>
@@ -4411,7 +4420,7 @@
         <v>23</v>
       </c>
       <c r="P44" s="20"/>
-      <c r="Q44" s="23"/>
+      <c r="Q44" s="28"/>
       <c r="R44" s="17" t="s">
         <v>23</v>
       </c>
@@ -4421,7 +4430,7 @@
       <c r="T44" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="U44" s="23"/>
+      <c r="U44" s="28"/>
       <c r="V44" s="17"/>
       <c r="W44" s="5">
         <f t="shared" si="3"/>
@@ -4461,7 +4470,7 @@
       <c r="J45" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="K45" s="23"/>
+      <c r="K45" s="28"/>
       <c r="L45" s="17" t="s">
         <v>23</v>
       </c>
@@ -4475,7 +4484,7 @@
         <v>23</v>
       </c>
       <c r="P45" s="20"/>
-      <c r="Q45" s="23"/>
+      <c r="Q45" s="28"/>
       <c r="R45" s="17" t="s">
         <v>31</v>
       </c>
@@ -4485,7 +4494,7 @@
       <c r="T45" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="U45" s="23"/>
+      <c r="U45" s="28"/>
       <c r="V45" s="17"/>
       <c r="W45" s="5">
         <f t="shared" si="3"/>
@@ -4525,7 +4534,7 @@
       <c r="J46" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="K46" s="23"/>
+      <c r="K46" s="28"/>
       <c r="L46" s="17" t="s">
         <v>23</v>
       </c>
@@ -4539,7 +4548,7 @@
         <v>23</v>
       </c>
       <c r="P46" s="20"/>
-      <c r="Q46" s="23"/>
+      <c r="Q46" s="28"/>
       <c r="R46" s="17" t="s">
         <v>31</v>
       </c>
@@ -4549,7 +4558,7 @@
       <c r="T46" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="U46" s="23"/>
+      <c r="U46" s="28"/>
       <c r="V46" s="17"/>
       <c r="W46" s="5">
         <f t="shared" si="3"/>
@@ -4589,7 +4598,7 @@
       <c r="J47" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="K47" s="23"/>
+      <c r="K47" s="28"/>
       <c r="L47" s="17" t="s">
         <v>23</v>
       </c>
@@ -4603,7 +4612,7 @@
         <v>23</v>
       </c>
       <c r="P47" s="20"/>
-      <c r="Q47" s="23"/>
+      <c r="Q47" s="28"/>
       <c r="R47" s="17" t="s">
         <v>23</v>
       </c>
@@ -4613,7 +4622,7 @@
       <c r="T47" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="U47" s="23"/>
+      <c r="U47" s="28"/>
       <c r="V47" s="17"/>
       <c r="W47" s="5">
         <f t="shared" si="3"/>
@@ -4653,7 +4662,7 @@
       <c r="J48" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="K48" s="23"/>
+      <c r="K48" s="28"/>
       <c r="L48" s="17" t="s">
         <v>23</v>
       </c>
@@ -4667,7 +4676,7 @@
         <v>23</v>
       </c>
       <c r="P48" s="20"/>
-      <c r="Q48" s="23"/>
+      <c r="Q48" s="28"/>
       <c r="R48" s="17" t="s">
         <v>23</v>
       </c>
@@ -4677,7 +4686,7 @@
       <c r="T48" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="U48" s="23"/>
+      <c r="U48" s="28"/>
       <c r="V48" s="17"/>
       <c r="W48" s="5">
         <f t="shared" si="3"/>
@@ -4717,7 +4726,7 @@
       <c r="J49" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="K49" s="23"/>
+      <c r="K49" s="28"/>
       <c r="L49" s="17" t="s">
         <v>23</v>
       </c>
@@ -4731,7 +4740,7 @@
         <v>23</v>
       </c>
       <c r="P49" s="20"/>
-      <c r="Q49" s="23"/>
+      <c r="Q49" s="28"/>
       <c r="R49" s="17" t="s">
         <v>23</v>
       </c>
@@ -4741,7 +4750,7 @@
       <c r="T49" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="U49" s="23"/>
+      <c r="U49" s="28"/>
       <c r="V49" s="17"/>
       <c r="W49" s="5">
         <f t="shared" si="3"/>
@@ -4781,7 +4790,7 @@
       <c r="J50" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="K50" s="23"/>
+      <c r="K50" s="28"/>
       <c r="L50" s="17" t="s">
         <v>23</v>
       </c>
@@ -4795,7 +4804,7 @@
         <v>23</v>
       </c>
       <c r="P50" s="20"/>
-      <c r="Q50" s="23"/>
+      <c r="Q50" s="28"/>
       <c r="R50" s="17" t="s">
         <v>23</v>
       </c>
@@ -4805,7 +4814,7 @@
       <c r="T50" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="U50" s="23"/>
+      <c r="U50" s="28"/>
       <c r="V50" s="17"/>
       <c r="W50" s="5">
         <f t="shared" si="3"/>
@@ -4845,7 +4854,7 @@
       <c r="J51" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="K51" s="23"/>
+      <c r="K51" s="28"/>
       <c r="L51" s="17" t="s">
         <v>23</v>
       </c>
@@ -4859,7 +4868,7 @@
         <v>23</v>
       </c>
       <c r="P51" s="20"/>
-      <c r="Q51" s="23"/>
+      <c r="Q51" s="28"/>
       <c r="R51" s="17" t="s">
         <v>23</v>
       </c>
@@ -4869,7 +4878,7 @@
       <c r="T51" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="U51" s="23"/>
+      <c r="U51" s="28"/>
       <c r="V51" s="17"/>
       <c r="W51" s="5">
         <f t="shared" si="3"/>
@@ -4899,7 +4908,7 @@
       <c r="H52" s="17"/>
       <c r="I52" s="20"/>
       <c r="J52" s="17"/>
-      <c r="K52" s="23"/>
+      <c r="K52" s="28"/>
       <c r="L52" s="17"/>
       <c r="M52" s="17"/>
       <c r="N52" s="17"/>
@@ -4907,7 +4916,7 @@
         <v>23</v>
       </c>
       <c r="P52" s="20"/>
-      <c r="Q52" s="23"/>
+      <c r="Q52" s="28"/>
       <c r="R52" s="17" t="s">
         <v>23</v>
       </c>
@@ -4917,7 +4926,7 @@
       <c r="T52" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="U52" s="23"/>
+      <c r="U52" s="28"/>
       <c r="V52" s="17"/>
       <c r="W52" s="5">
         <f t="shared" si="3"/>
@@ -4949,13 +4958,13 @@
       <c r="H53" s="17"/>
       <c r="I53" s="21"/>
       <c r="J53" s="17"/>
-      <c r="K53" s="24"/>
+      <c r="K53" s="29"/>
       <c r="L53" s="17"/>
       <c r="M53" s="17"/>
       <c r="N53" s="17"/>
       <c r="O53" s="17"/>
       <c r="P53" s="21"/>
-      <c r="Q53" s="24"/>
+      <c r="Q53" s="29"/>
       <c r="R53" s="17"/>
       <c r="S53" s="17" t="s">
         <v>23</v>
@@ -4963,7 +4972,7 @@
       <c r="T53" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="U53" s="24"/>
+      <c r="U53" s="29"/>
       <c r="V53" s="17"/>
       <c r="W53" s="5">
         <f t="shared" si="3"/>
@@ -4976,6 +4985,9 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="Y3:Z3"/>
+    <mergeCell ref="Y8:AB8"/>
+    <mergeCell ref="Y16:AB16"/>
     <mergeCell ref="I5:I53"/>
     <mergeCell ref="A1:X1"/>
     <mergeCell ref="A2:X2"/>
@@ -4990,9 +5002,6 @@
     <mergeCell ref="K5:K53"/>
     <mergeCell ref="Q5:Q53"/>
     <mergeCell ref="U5:U53"/>
-    <mergeCell ref="Y3:Z3"/>
-    <mergeCell ref="Y8:AB8"/>
-    <mergeCell ref="Y16:AB16"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:B29">
     <cfRule type="duplicateValues" dxfId="55" priority="14"/>
@@ -5098,101 +5107,101 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:41" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
-      <c r="J1" s="28"/>
-      <c r="K1" s="28"/>
-      <c r="L1" s="28"/>
-      <c r="M1" s="28"/>
-      <c r="N1" s="28"/>
-      <c r="O1" s="28"/>
-      <c r="P1" s="28"/>
-      <c r="Q1" s="28"/>
-      <c r="R1" s="28"/>
-      <c r="S1" s="28"/>
-      <c r="T1" s="28"/>
-      <c r="U1" s="28"/>
-      <c r="V1" s="28"/>
-      <c r="W1" s="28"/>
-      <c r="X1" s="28"/>
-      <c r="Y1" s="28"/>
-      <c r="Z1" s="28"/>
-      <c r="AA1" s="28"/>
-      <c r="AB1" s="28"/>
-      <c r="AC1" s="28"/>
-      <c r="AD1" s="28"/>
-      <c r="AE1" s="28"/>
-      <c r="AF1" s="28"/>
-      <c r="AG1" s="28"/>
-      <c r="AH1" s="28"/>
-      <c r="AI1" s="28"/>
-      <c r="AJ1" s="28"/>
-      <c r="AK1" s="28"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="22"/>
+      <c r="L1" s="22"/>
+      <c r="M1" s="22"/>
+      <c r="N1" s="22"/>
+      <c r="O1" s="22"/>
+      <c r="P1" s="22"/>
+      <c r="Q1" s="22"/>
+      <c r="R1" s="22"/>
+      <c r="S1" s="22"/>
+      <c r="T1" s="22"/>
+      <c r="U1" s="22"/>
+      <c r="V1" s="22"/>
+      <c r="W1" s="22"/>
+      <c r="X1" s="22"/>
+      <c r="Y1" s="22"/>
+      <c r="Z1" s="22"/>
+      <c r="AA1" s="22"/>
+      <c r="AB1" s="22"/>
+      <c r="AC1" s="22"/>
+      <c r="AD1" s="22"/>
+      <c r="AE1" s="22"/>
+      <c r="AF1" s="22"/>
+      <c r="AG1" s="22"/>
+      <c r="AH1" s="22"/>
+      <c r="AI1" s="22"/>
+      <c r="AJ1" s="22"/>
+      <c r="AK1" s="22"/>
     </row>
     <row r="2" spans="1:41" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A2" s="29" t="s">
-        <v>21</v>
-      </c>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
-      <c r="I2" s="29"/>
-      <c r="J2" s="29"/>
-      <c r="K2" s="29"/>
-      <c r="L2" s="29"/>
-      <c r="M2" s="29"/>
-      <c r="N2" s="29"/>
-      <c r="O2" s="29"/>
-      <c r="P2" s="29"/>
-      <c r="Q2" s="29"/>
-      <c r="R2" s="29"/>
-      <c r="S2" s="29"/>
-      <c r="T2" s="29"/>
-      <c r="U2" s="29"/>
-      <c r="V2" s="29"/>
-      <c r="W2" s="29"/>
-      <c r="X2" s="29"/>
-      <c r="Y2" s="29"/>
-      <c r="Z2" s="29"/>
-      <c r="AA2" s="29"/>
-      <c r="AB2" s="29"/>
-      <c r="AC2" s="29"/>
-      <c r="AD2" s="29"/>
-      <c r="AE2" s="29"/>
-      <c r="AF2" s="29"/>
-      <c r="AG2" s="29"/>
-      <c r="AH2" s="29"/>
-      <c r="AI2" s="29"/>
-      <c r="AJ2" s="29"/>
-      <c r="AK2" s="29"/>
+      <c r="A2" s="23" t="s">
+        <v>132</v>
+      </c>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
+      <c r="I2" s="23"/>
+      <c r="J2" s="23"/>
+      <c r="K2" s="23"/>
+      <c r="L2" s="23"/>
+      <c r="M2" s="23"/>
+      <c r="N2" s="23"/>
+      <c r="O2" s="23"/>
+      <c r="P2" s="23"/>
+      <c r="Q2" s="23"/>
+      <c r="R2" s="23"/>
+      <c r="S2" s="23"/>
+      <c r="T2" s="23"/>
+      <c r="U2" s="23"/>
+      <c r="V2" s="23"/>
+      <c r="W2" s="23"/>
+      <c r="X2" s="23"/>
+      <c r="Y2" s="23"/>
+      <c r="Z2" s="23"/>
+      <c r="AA2" s="23"/>
+      <c r="AB2" s="23"/>
+      <c r="AC2" s="23"/>
+      <c r="AD2" s="23"/>
+      <c r="AE2" s="23"/>
+      <c r="AF2" s="23"/>
+      <c r="AG2" s="23"/>
+      <c r="AH2" s="23"/>
+      <c r="AI2" s="23"/>
+      <c r="AJ2" s="23"/>
+      <c r="AK2" s="23"/>
     </row>
     <row r="3" spans="1:41" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="30" t="s">
+      <c r="A3" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="30" t="s">
+      <c r="B3" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="30" t="s">
+      <c r="C3" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="30" t="s">
+      <c r="D3" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="30" t="s">
+      <c r="E3" s="24" t="s">
         <v>4</v>
       </c>
       <c r="F3" s="2" t="str">
@@ -5315,25 +5324,25 @@
         <f t="shared" si="0"/>
         <v>Mon</v>
       </c>
-      <c r="AJ3" s="32" t="s">
+      <c r="AJ3" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="AK3" s="32" t="s">
+      <c r="AK3" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="AL3" s="25" t="s">
+      <c r="AL3" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="AM3" s="26"/>
+      <c r="AM3" s="31"/>
       <c r="AN3" s="3"/>
       <c r="AO3" s="3"/>
     </row>
     <row r="4" spans="1:41" ht="36" x14ac:dyDescent="0.25">
-      <c r="A4" s="31"/>
-      <c r="B4" s="31"/>
-      <c r="C4" s="31"/>
-      <c r="D4" s="31"/>
-      <c r="E4" s="31"/>
+      <c r="A4" s="25"/>
+      <c r="B4" s="25"/>
+      <c r="C4" s="25"/>
+      <c r="D4" s="25"/>
+      <c r="E4" s="25"/>
       <c r="F4" s="14">
         <v>45536</v>
       </c>
@@ -5424,8 +5433,8 @@
       <c r="AI4" s="14">
         <v>45565</v>
       </c>
-      <c r="AJ4" s="32"/>
-      <c r="AK4" s="32"/>
+      <c r="AJ4" s="26"/>
+      <c r="AK4" s="26"/>
       <c r="AL4" s="4" t="s">
         <v>7</v>
       </c>
@@ -5880,12 +5889,12 @@
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="AL8" s="25" t="s">
+      <c r="AL8" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="AM8" s="26"/>
-      <c r="AN8" s="26"/>
-      <c r="AO8" s="27"/>
+      <c r="AM8" s="31"/>
+      <c r="AN8" s="31"/>
+      <c r="AO8" s="32"/>
     </row>
     <row r="9" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A9" s="8">
@@ -6661,12 +6670,12 @@
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="AL15" s="25" t="s">
+      <c r="AL15" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="AM15" s="26"/>
-      <c r="AN15" s="26"/>
-      <c r="AO15" s="27"/>
+      <c r="AM15" s="31"/>
+      <c r="AN15" s="31"/>
+      <c r="AO15" s="32"/>
     </row>
     <row r="16" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A16" s="8">
@@ -10257,6 +10266,10 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="AL3:AM3"/>
+    <mergeCell ref="AL8:AO8"/>
+    <mergeCell ref="AL15:AO15"/>
+    <mergeCell ref="V5:V50"/>
     <mergeCell ref="F5:F50"/>
     <mergeCell ref="M5:M50"/>
     <mergeCell ref="A1:AK1"/>
@@ -10271,10 +10284,6 @@
     <mergeCell ref="T5:T50"/>
     <mergeCell ref="AA5:AA50"/>
     <mergeCell ref="AH5:AH50"/>
-    <mergeCell ref="AL3:AM3"/>
-    <mergeCell ref="AL8:AO8"/>
-    <mergeCell ref="AL15:AO15"/>
-    <mergeCell ref="V5:V50"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:B27">
     <cfRule type="duplicateValues" dxfId="41" priority="28"/>
@@ -10380,103 +10389,103 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
-      <c r="J1" s="28"/>
-      <c r="K1" s="28"/>
-      <c r="L1" s="28"/>
-      <c r="M1" s="28"/>
-      <c r="N1" s="28"/>
-      <c r="O1" s="28"/>
-      <c r="P1" s="28"/>
-      <c r="Q1" s="28"/>
-      <c r="R1" s="28"/>
-      <c r="S1" s="28"/>
-      <c r="T1" s="28"/>
-      <c r="U1" s="28"/>
-      <c r="V1" s="28"/>
-      <c r="W1" s="28"/>
-      <c r="X1" s="28"/>
-      <c r="Y1" s="28"/>
-      <c r="Z1" s="28"/>
-      <c r="AA1" s="28"/>
-      <c r="AB1" s="28"/>
-      <c r="AC1" s="28"/>
-      <c r="AD1" s="28"/>
-      <c r="AE1" s="28"/>
-      <c r="AF1" s="28"/>
-      <c r="AG1" s="28"/>
-      <c r="AH1" s="28"/>
-      <c r="AI1" s="28"/>
-      <c r="AJ1" s="28"/>
-      <c r="AK1" s="28"/>
-      <c r="AL1" s="28"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="22"/>
+      <c r="L1" s="22"/>
+      <c r="M1" s="22"/>
+      <c r="N1" s="22"/>
+      <c r="O1" s="22"/>
+      <c r="P1" s="22"/>
+      <c r="Q1" s="22"/>
+      <c r="R1" s="22"/>
+      <c r="S1" s="22"/>
+      <c r="T1" s="22"/>
+      <c r="U1" s="22"/>
+      <c r="V1" s="22"/>
+      <c r="W1" s="22"/>
+      <c r="X1" s="22"/>
+      <c r="Y1" s="22"/>
+      <c r="Z1" s="22"/>
+      <c r="AA1" s="22"/>
+      <c r="AB1" s="22"/>
+      <c r="AC1" s="22"/>
+      <c r="AD1" s="22"/>
+      <c r="AE1" s="22"/>
+      <c r="AF1" s="22"/>
+      <c r="AG1" s="22"/>
+      <c r="AH1" s="22"/>
+      <c r="AI1" s="22"/>
+      <c r="AJ1" s="22"/>
+      <c r="AK1" s="22"/>
+      <c r="AL1" s="22"/>
     </row>
     <row r="2" spans="1:42" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A2" s="29" t="s">
-        <v>21</v>
-      </c>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
-      <c r="I2" s="29"/>
-      <c r="J2" s="29"/>
-      <c r="K2" s="29"/>
-      <c r="L2" s="29"/>
-      <c r="M2" s="29"/>
-      <c r="N2" s="29"/>
-      <c r="O2" s="29"/>
-      <c r="P2" s="29"/>
-      <c r="Q2" s="29"/>
-      <c r="R2" s="29"/>
-      <c r="S2" s="29"/>
-      <c r="T2" s="29"/>
-      <c r="U2" s="29"/>
-      <c r="V2" s="29"/>
-      <c r="W2" s="29"/>
-      <c r="X2" s="29"/>
-      <c r="Y2" s="29"/>
-      <c r="Z2" s="29"/>
-      <c r="AA2" s="29"/>
-      <c r="AB2" s="29"/>
-      <c r="AC2" s="29"/>
-      <c r="AD2" s="29"/>
-      <c r="AE2" s="29"/>
-      <c r="AF2" s="29"/>
-      <c r="AG2" s="29"/>
-      <c r="AH2" s="29"/>
-      <c r="AI2" s="29"/>
-      <c r="AJ2" s="29"/>
-      <c r="AK2" s="29"/>
-      <c r="AL2" s="29"/>
+      <c r="A2" s="23" t="s">
+        <v>131</v>
+      </c>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
+      <c r="I2" s="23"/>
+      <c r="J2" s="23"/>
+      <c r="K2" s="23"/>
+      <c r="L2" s="23"/>
+      <c r="M2" s="23"/>
+      <c r="N2" s="23"/>
+      <c r="O2" s="23"/>
+      <c r="P2" s="23"/>
+      <c r="Q2" s="23"/>
+      <c r="R2" s="23"/>
+      <c r="S2" s="23"/>
+      <c r="T2" s="23"/>
+      <c r="U2" s="23"/>
+      <c r="V2" s="23"/>
+      <c r="W2" s="23"/>
+      <c r="X2" s="23"/>
+      <c r="Y2" s="23"/>
+      <c r="Z2" s="23"/>
+      <c r="AA2" s="23"/>
+      <c r="AB2" s="23"/>
+      <c r="AC2" s="23"/>
+      <c r="AD2" s="23"/>
+      <c r="AE2" s="23"/>
+      <c r="AF2" s="23"/>
+      <c r="AG2" s="23"/>
+      <c r="AH2" s="23"/>
+      <c r="AI2" s="23"/>
+      <c r="AJ2" s="23"/>
+      <c r="AK2" s="23"/>
+      <c r="AL2" s="23"/>
     </row>
     <row r="3" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="30" t="s">
+      <c r="A3" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="30" t="s">
+      <c r="B3" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="30" t="s">
+      <c r="C3" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="30" t="s">
+      <c r="D3" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="30" t="s">
+      <c r="E3" s="24" t="s">
         <v>4</v>
       </c>
       <c r="F3" s="2" t="str">
@@ -10603,25 +10612,25 @@
         <f t="shared" si="0"/>
         <v>Thu</v>
       </c>
-      <c r="AK3" s="32" t="s">
+      <c r="AK3" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="AL3" s="32" t="s">
+      <c r="AL3" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="AM3" s="25" t="s">
+      <c r="AM3" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="AN3" s="26"/>
+      <c r="AN3" s="31"/>
       <c r="AO3" s="3"/>
       <c r="AP3" s="3"/>
     </row>
     <row r="4" spans="1:42" ht="34.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="31"/>
-      <c r="B4" s="31"/>
-      <c r="C4" s="31"/>
-      <c r="D4" s="31"/>
-      <c r="E4" s="31"/>
+      <c r="A4" s="25"/>
+      <c r="B4" s="25"/>
+      <c r="C4" s="25"/>
+      <c r="D4" s="25"/>
+      <c r="E4" s="25"/>
       <c r="F4" s="14">
         <v>45566</v>
       </c>
@@ -10715,8 +10724,8 @@
       <c r="AJ4" s="14">
         <v>45596</v>
       </c>
-      <c r="AK4" s="32"/>
-      <c r="AL4" s="32"/>
+      <c r="AK4" s="26"/>
+      <c r="AL4" s="26"/>
       <c r="AM4" s="4" t="s">
         <v>7</v>
       </c>
@@ -11195,12 +11204,12 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="AM8" s="25" t="s">
+      <c r="AM8" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="AN8" s="26"/>
-      <c r="AO8" s="26"/>
-      <c r="AP8" s="27"/>
+      <c r="AN8" s="31"/>
+      <c r="AO8" s="31"/>
+      <c r="AP8" s="32"/>
     </row>
     <row r="9" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A9" s="8">
@@ -12025,12 +12034,12 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AM15" s="25" t="s">
+      <c r="AM15" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="AN15" s="26"/>
-      <c r="AO15" s="26"/>
-      <c r="AP15" s="27"/>
+      <c r="AN15" s="31"/>
+      <c r="AO15" s="31"/>
+      <c r="AP15" s="32"/>
     </row>
     <row r="16" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A16" s="8">
@@ -16048,101 +16057,101 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:41" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
-      <c r="J1" s="28"/>
-      <c r="K1" s="28"/>
-      <c r="L1" s="28"/>
-      <c r="M1" s="28"/>
-      <c r="N1" s="28"/>
-      <c r="O1" s="28"/>
-      <c r="P1" s="28"/>
-      <c r="Q1" s="28"/>
-      <c r="R1" s="28"/>
-      <c r="S1" s="28"/>
-      <c r="T1" s="28"/>
-      <c r="U1" s="28"/>
-      <c r="V1" s="28"/>
-      <c r="W1" s="28"/>
-      <c r="X1" s="28"/>
-      <c r="Y1" s="28"/>
-      <c r="Z1" s="28"/>
-      <c r="AA1" s="28"/>
-      <c r="AB1" s="28"/>
-      <c r="AC1" s="28"/>
-      <c r="AD1" s="28"/>
-      <c r="AE1" s="28"/>
-      <c r="AF1" s="28"/>
-      <c r="AG1" s="28"/>
-      <c r="AH1" s="28"/>
-      <c r="AI1" s="28"/>
-      <c r="AJ1" s="28"/>
-      <c r="AK1" s="28"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="22"/>
+      <c r="L1" s="22"/>
+      <c r="M1" s="22"/>
+      <c r="N1" s="22"/>
+      <c r="O1" s="22"/>
+      <c r="P1" s="22"/>
+      <c r="Q1" s="22"/>
+      <c r="R1" s="22"/>
+      <c r="S1" s="22"/>
+      <c r="T1" s="22"/>
+      <c r="U1" s="22"/>
+      <c r="V1" s="22"/>
+      <c r="W1" s="22"/>
+      <c r="X1" s="22"/>
+      <c r="Y1" s="22"/>
+      <c r="Z1" s="22"/>
+      <c r="AA1" s="22"/>
+      <c r="AB1" s="22"/>
+      <c r="AC1" s="22"/>
+      <c r="AD1" s="22"/>
+      <c r="AE1" s="22"/>
+      <c r="AF1" s="22"/>
+      <c r="AG1" s="22"/>
+      <c r="AH1" s="22"/>
+      <c r="AI1" s="22"/>
+      <c r="AJ1" s="22"/>
+      <c r="AK1" s="22"/>
     </row>
     <row r="2" spans="1:41" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A2" s="29" t="s">
-        <v>21</v>
-      </c>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
-      <c r="I2" s="29"/>
-      <c r="J2" s="29"/>
-      <c r="K2" s="29"/>
-      <c r="L2" s="29"/>
-      <c r="M2" s="29"/>
-      <c r="N2" s="29"/>
-      <c r="O2" s="29"/>
-      <c r="P2" s="29"/>
-      <c r="Q2" s="29"/>
-      <c r="R2" s="29"/>
-      <c r="S2" s="29"/>
-      <c r="T2" s="29"/>
-      <c r="U2" s="29"/>
-      <c r="V2" s="29"/>
-      <c r="W2" s="29"/>
-      <c r="X2" s="29"/>
-      <c r="Y2" s="29"/>
-      <c r="Z2" s="29"/>
-      <c r="AA2" s="29"/>
-      <c r="AB2" s="29"/>
-      <c r="AC2" s="29"/>
-      <c r="AD2" s="29"/>
-      <c r="AE2" s="29"/>
-      <c r="AF2" s="29"/>
-      <c r="AG2" s="29"/>
-      <c r="AH2" s="29"/>
-      <c r="AI2" s="29"/>
-      <c r="AJ2" s="29"/>
-      <c r="AK2" s="29"/>
+      <c r="A2" s="23" t="s">
+        <v>130</v>
+      </c>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
+      <c r="I2" s="23"/>
+      <c r="J2" s="23"/>
+      <c r="K2" s="23"/>
+      <c r="L2" s="23"/>
+      <c r="M2" s="23"/>
+      <c r="N2" s="23"/>
+      <c r="O2" s="23"/>
+      <c r="P2" s="23"/>
+      <c r="Q2" s="23"/>
+      <c r="R2" s="23"/>
+      <c r="S2" s="23"/>
+      <c r="T2" s="23"/>
+      <c r="U2" s="23"/>
+      <c r="V2" s="23"/>
+      <c r="W2" s="23"/>
+      <c r="X2" s="23"/>
+      <c r="Y2" s="23"/>
+      <c r="Z2" s="23"/>
+      <c r="AA2" s="23"/>
+      <c r="AB2" s="23"/>
+      <c r="AC2" s="23"/>
+      <c r="AD2" s="23"/>
+      <c r="AE2" s="23"/>
+      <c r="AF2" s="23"/>
+      <c r="AG2" s="23"/>
+      <c r="AH2" s="23"/>
+      <c r="AI2" s="23"/>
+      <c r="AJ2" s="23"/>
+      <c r="AK2" s="23"/>
     </row>
     <row r="3" spans="1:41" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="30" t="s">
+      <c r="A3" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="30" t="s">
+      <c r="B3" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="30" t="s">
+      <c r="C3" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="30" t="s">
+      <c r="D3" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="30" t="s">
+      <c r="E3" s="24" t="s">
         <v>4</v>
       </c>
       <c r="F3" s="2" t="str">
@@ -16265,25 +16274,25 @@
         <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
-      <c r="AJ3" s="32" t="s">
+      <c r="AJ3" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="AK3" s="32" t="s">
+      <c r="AK3" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="AL3" s="25" t="s">
+      <c r="AL3" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="AM3" s="26"/>
+      <c r="AM3" s="31"/>
       <c r="AN3" s="3"/>
       <c r="AO3" s="3"/>
     </row>
     <row r="4" spans="1:41" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="31"/>
-      <c r="B4" s="31"/>
-      <c r="C4" s="31"/>
-      <c r="D4" s="31"/>
-      <c r="E4" s="31"/>
+      <c r="A4" s="25"/>
+      <c r="B4" s="25"/>
+      <c r="C4" s="25"/>
+      <c r="D4" s="25"/>
+      <c r="E4" s="25"/>
       <c r="F4" s="14">
         <v>45597</v>
       </c>
@@ -16374,8 +16383,8 @@
       <c r="AI4" s="14">
         <v>45626</v>
       </c>
-      <c r="AJ4" s="32"/>
-      <c r="AK4" s="32"/>
+      <c r="AJ4" s="26"/>
+      <c r="AK4" s="26"/>
       <c r="AL4" s="4" t="s">
         <v>7</v>
       </c>
@@ -16425,7 +16434,7 @@
       <c r="M5" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="N5" s="22" t="s">
+      <c r="N5" s="27" t="s">
         <v>129</v>
       </c>
       <c r="O5" s="19" t="s">
@@ -16546,7 +16555,7 @@
       <c r="M6" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="N6" s="23"/>
+      <c r="N6" s="28"/>
       <c r="O6" s="20"/>
       <c r="P6" s="17" t="s">
         <v>23</v>
@@ -16657,7 +16666,7 @@
       <c r="M7" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="N7" s="23"/>
+      <c r="N7" s="28"/>
       <c r="O7" s="20"/>
       <c r="P7" s="17" t="s">
         <v>23</v>
@@ -16764,7 +16773,7 @@
       <c r="M8" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="N8" s="23"/>
+      <c r="N8" s="28"/>
       <c r="O8" s="20"/>
       <c r="P8" s="17" t="s">
         <v>23</v>
@@ -16828,12 +16837,12 @@
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="AL8" s="25" t="s">
+      <c r="AL8" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="AM8" s="26"/>
-      <c r="AN8" s="26"/>
-      <c r="AO8" s="27"/>
+      <c r="AM8" s="31"/>
+      <c r="AN8" s="31"/>
+      <c r="AO8" s="32"/>
     </row>
     <row r="9" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
@@ -16873,7 +16882,7 @@
       <c r="M9" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="N9" s="23"/>
+      <c r="N9" s="28"/>
       <c r="O9" s="20"/>
       <c r="P9" s="17" t="s">
         <v>23</v>
@@ -16986,7 +16995,7 @@
       <c r="M10" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="N10" s="23"/>
+      <c r="N10" s="28"/>
       <c r="O10" s="20"/>
       <c r="P10" s="17" t="s">
         <v>23</v>
@@ -17102,7 +17111,7 @@
       <c r="M11" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="N11" s="23"/>
+      <c r="N11" s="28"/>
       <c r="O11" s="20"/>
       <c r="P11" s="17" t="s">
         <v>23</v>
@@ -17218,7 +17227,7 @@
       <c r="M12" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="N12" s="23"/>
+      <c r="N12" s="28"/>
       <c r="O12" s="20"/>
       <c r="P12" s="17" t="s">
         <v>23</v>
@@ -17323,7 +17332,7 @@
       <c r="M13" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="N13" s="23"/>
+      <c r="N13" s="28"/>
       <c r="O13" s="20"/>
       <c r="P13" s="17" t="s">
         <v>23</v>
@@ -17428,7 +17437,7 @@
       <c r="M14" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="N14" s="23"/>
+      <c r="N14" s="28"/>
       <c r="O14" s="20"/>
       <c r="P14" s="17" t="s">
         <v>23</v>
@@ -17533,7 +17542,7 @@
       <c r="M15" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="N15" s="23"/>
+      <c r="N15" s="28"/>
       <c r="O15" s="20"/>
       <c r="P15" s="17" t="s">
         <v>23</v>
@@ -17595,12 +17604,12 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AL15" s="25" t="s">
+      <c r="AL15" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="AM15" s="26"/>
-      <c r="AN15" s="26"/>
-      <c r="AO15" s="27"/>
+      <c r="AM15" s="31"/>
+      <c r="AN15" s="31"/>
+      <c r="AO15" s="32"/>
     </row>
     <row r="16" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A16" s="8">
@@ -17640,7 +17649,7 @@
       <c r="M16" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="N16" s="23"/>
+      <c r="N16" s="28"/>
       <c r="O16" s="20"/>
       <c r="P16" s="17" t="s">
         <v>31</v>
@@ -17753,7 +17762,7 @@
       <c r="M17" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="N17" s="23"/>
+      <c r="N17" s="28"/>
       <c r="O17" s="20"/>
       <c r="P17" s="17" t="s">
         <v>23</v>
@@ -17869,7 +17878,7 @@
       <c r="M18" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="N18" s="23"/>
+      <c r="N18" s="28"/>
       <c r="O18" s="20"/>
       <c r="P18" s="17" t="s">
         <v>23</v>
@@ -17985,7 +17994,7 @@
       <c r="M19" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="N19" s="23"/>
+      <c r="N19" s="28"/>
       <c r="O19" s="20"/>
       <c r="P19" s="17" t="s">
         <v>23</v>
@@ -18090,7 +18099,7 @@
       <c r="M20" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="N20" s="23"/>
+      <c r="N20" s="28"/>
       <c r="O20" s="20"/>
       <c r="P20" s="17" t="s">
         <v>23</v>
@@ -18191,7 +18200,7 @@
       <c r="M21" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="N21" s="23"/>
+      <c r="N21" s="28"/>
       <c r="O21" s="20"/>
       <c r="P21" s="17" t="s">
         <v>23</v>
@@ -18292,7 +18301,7 @@
       <c r="M22" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="N22" s="23"/>
+      <c r="N22" s="28"/>
       <c r="O22" s="20"/>
       <c r="P22" s="17" t="s">
         <v>23</v>
@@ -18393,7 +18402,7 @@
       <c r="M23" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="N23" s="23"/>
+      <c r="N23" s="28"/>
       <c r="O23" s="20"/>
       <c r="P23" s="17" t="s">
         <v>23</v>
@@ -18494,7 +18503,7 @@
       <c r="M24" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="N24" s="23"/>
+      <c r="N24" s="28"/>
       <c r="O24" s="20"/>
       <c r="P24" s="17" t="s">
         <v>23</v>
@@ -18595,7 +18604,7 @@
       <c r="M25" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="N25" s="23"/>
+      <c r="N25" s="28"/>
       <c r="O25" s="20"/>
       <c r="P25" s="17" t="s">
         <v>23</v>
@@ -18696,7 +18705,7 @@
       <c r="M26" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="N26" s="23"/>
+      <c r="N26" s="28"/>
       <c r="O26" s="20"/>
       <c r="P26" s="17" t="s">
         <v>23</v>
@@ -18797,7 +18806,7 @@
       <c r="M27" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="N27" s="23"/>
+      <c r="N27" s="28"/>
       <c r="O27" s="20"/>
       <c r="P27" s="17" t="s">
         <v>23</v>
@@ -18898,7 +18907,7 @@
       <c r="M28" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="N28" s="23"/>
+      <c r="N28" s="28"/>
       <c r="O28" s="20"/>
       <c r="P28" s="17" t="s">
         <v>23</v>
@@ -18999,7 +19008,7 @@
       <c r="M29" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="N29" s="23"/>
+      <c r="N29" s="28"/>
       <c r="O29" s="20"/>
       <c r="P29" s="17" t="s">
         <v>23</v>
@@ -19100,7 +19109,7 @@
       <c r="M30" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="N30" s="23"/>
+      <c r="N30" s="28"/>
       <c r="O30" s="20"/>
       <c r="P30" s="17" t="s">
         <v>23</v>
@@ -19201,7 +19210,7 @@
       <c r="M31" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="N31" s="23"/>
+      <c r="N31" s="28"/>
       <c r="O31" s="20"/>
       <c r="P31" s="17" t="s">
         <v>31</v>
@@ -19302,7 +19311,7 @@
       <c r="M32" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="N32" s="23"/>
+      <c r="N32" s="28"/>
       <c r="O32" s="20"/>
       <c r="P32" s="17" t="s">
         <v>23</v>
@@ -19403,7 +19412,7 @@
       <c r="M33" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="N33" s="23"/>
+      <c r="N33" s="28"/>
       <c r="O33" s="20"/>
       <c r="P33" s="17" t="s">
         <v>23</v>
@@ -19504,7 +19513,7 @@
       <c r="M34" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="N34" s="23"/>
+      <c r="N34" s="28"/>
       <c r="O34" s="20"/>
       <c r="P34" s="17" t="s">
         <v>31</v>
@@ -19605,7 +19614,7 @@
       <c r="M35" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="N35" s="23"/>
+      <c r="N35" s="28"/>
       <c r="O35" s="20"/>
       <c r="P35" s="17" t="s">
         <v>23</v>
@@ -19706,7 +19715,7 @@
       <c r="M36" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="N36" s="23"/>
+      <c r="N36" s="28"/>
       <c r="O36" s="20"/>
       <c r="P36" s="17" t="s">
         <v>23</v>
@@ -19807,7 +19816,7 @@
       <c r="M37" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="N37" s="23"/>
+      <c r="N37" s="28"/>
       <c r="O37" s="20"/>
       <c r="P37" s="17" t="s">
         <v>23</v>
@@ -19908,7 +19917,7 @@
       <c r="M38" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="N38" s="23"/>
+      <c r="N38" s="28"/>
       <c r="O38" s="20"/>
       <c r="P38" s="17" t="s">
         <v>23</v>
@@ -20009,7 +20018,7 @@
       <c r="M39" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="N39" s="23"/>
+      <c r="N39" s="28"/>
       <c r="O39" s="20"/>
       <c r="P39" s="17" t="s">
         <v>23</v>
@@ -20110,7 +20119,7 @@
       <c r="M40" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="N40" s="23"/>
+      <c r="N40" s="28"/>
       <c r="O40" s="20"/>
       <c r="P40" s="17" t="s">
         <v>31</v>
@@ -20211,7 +20220,7 @@
       <c r="M41" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="N41" s="23"/>
+      <c r="N41" s="28"/>
       <c r="O41" s="20"/>
       <c r="P41" s="17" t="s">
         <v>23</v>
@@ -20312,7 +20321,7 @@
       <c r="M42" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="N42" s="23"/>
+      <c r="N42" s="28"/>
       <c r="O42" s="20"/>
       <c r="P42" s="17" t="s">
         <v>23</v>
@@ -20413,7 +20422,7 @@
       <c r="M43" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="N43" s="23"/>
+      <c r="N43" s="28"/>
       <c r="O43" s="20"/>
       <c r="P43" s="17" t="s">
         <v>23</v>
@@ -20514,7 +20523,7 @@
       <c r="M44" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="N44" s="23"/>
+      <c r="N44" s="28"/>
       <c r="O44" s="20"/>
       <c r="P44" s="17" t="s">
         <v>31</v>
@@ -20615,7 +20624,7 @@
       <c r="M45" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="N45" s="23"/>
+      <c r="N45" s="28"/>
       <c r="O45" s="20"/>
       <c r="P45" s="17" t="s">
         <v>31</v>
@@ -20716,7 +20725,7 @@
       <c r="M46" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="N46" s="23"/>
+      <c r="N46" s="28"/>
       <c r="O46" s="20"/>
       <c r="P46" s="17" t="s">
         <v>23</v>
@@ -20817,7 +20826,7 @@
       <c r="M47" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="N47" s="23"/>
+      <c r="N47" s="28"/>
       <c r="O47" s="20"/>
       <c r="P47" s="17" t="s">
         <v>23</v>
@@ -20918,7 +20927,7 @@
       <c r="M48" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="N48" s="23"/>
+      <c r="N48" s="28"/>
       <c r="O48" s="20"/>
       <c r="P48" s="17" t="s">
         <v>23</v>
@@ -21019,7 +21028,7 @@
       <c r="M49" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="N49" s="23"/>
+      <c r="N49" s="28"/>
       <c r="O49" s="20"/>
       <c r="P49" s="17" t="s">
         <v>23</v>
@@ -21120,7 +21129,7 @@
       <c r="M50" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="N50" s="24"/>
+      <c r="N50" s="29"/>
       <c r="O50" s="21"/>
       <c r="P50" s="17" t="s">
         <v>23</v>
@@ -21185,11 +21194,9 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="V5:V50"/>
-    <mergeCell ref="AC5:AC50"/>
-    <mergeCell ref="AL3:AM3"/>
-    <mergeCell ref="AL8:AO8"/>
-    <mergeCell ref="AL15:AO15"/>
+    <mergeCell ref="N5:N50"/>
+    <mergeCell ref="H5:H50"/>
+    <mergeCell ref="O5:O50"/>
     <mergeCell ref="A1:AK1"/>
     <mergeCell ref="A2:AK2"/>
     <mergeCell ref="A3:A4"/>
@@ -21199,9 +21206,11 @@
     <mergeCell ref="E3:E4"/>
     <mergeCell ref="AJ3:AJ4"/>
     <mergeCell ref="AK3:AK4"/>
-    <mergeCell ref="N5:N50"/>
-    <mergeCell ref="H5:H50"/>
-    <mergeCell ref="O5:O50"/>
+    <mergeCell ref="V5:V50"/>
+    <mergeCell ref="AC5:AC50"/>
+    <mergeCell ref="AL3:AM3"/>
+    <mergeCell ref="AL8:AO8"/>
+    <mergeCell ref="AL15:AO15"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:B27">
     <cfRule type="duplicateValues" dxfId="13" priority="42"/>
